--- a/data/trans_bre/IQ09_D_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ09_D_R3-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que llevan más tiempo (cuartil más desfavorable) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que llevan más tiempo (cuartil más desfavorable: más de 2161 días) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,161 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-18,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-19,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>239,52%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-18.00350773992662</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-19.917996822814</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>37.2716862171546</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>2.395228792563191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-59,96; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-53,57; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,52; 83,49</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-59.96263161288014</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-53.57085661962956</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-15.52279552470997</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>83.48644192938035</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-25,16</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,81</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,61</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-25,85</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>107,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-46,08%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-58,1; -8,2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-13,41; 36,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-40,63; 23,34</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-57,95; -7,4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-25.15884658231428</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.809447921889817</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-9.608063728858717</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-25.85425078493925</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.077019853988777</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.460805582666834</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>16,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-19,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-45,87%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-58.1045626076226</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-13.40677462963301</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-40.62790828247115</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-57.95013692308257</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-53,29; 60,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 42,1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-69,58; 39,6</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-8.19664751436482</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>36.80669428796284</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>23.33995903079549</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-7.398802687771185</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +781,257 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-9,47</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-31,89</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-10,38</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,91</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>16.00097025070243</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>8.596851545922824</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-19.21740418960027</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.6558953100226274</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="n">
+        <v>-0.4586709917100471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-38,06; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-64,0; -8,2</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-43,34; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-37,09; 54,15</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-53.28967189205572</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="n">
+        <v>-69.57899993586852</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>60.68292775892107</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>42.09606363064582</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>39.59804321176418</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-9.470983920359092</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-31.89165347158836</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-10.38005893419929</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6.913248637263342</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.2258435017394578</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-38.06299500770533</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-63.99876470279926</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-43.34229506857613</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-37.08501386538527</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-8.204073709514587</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>54.15412383565184</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,72</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-46,88%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-45,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-51,2%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-9,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-27,8; 12,24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-17,59; 7,67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-17,39; 9,24</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-27,0; 20,78</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 222,76</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 125,79</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-73,56; 140,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-8.717846516673578</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-6.180163843580814</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-4.810294592019301</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.835173449622475</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.4688212380081302</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.4530603166831068</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.5120406506063031</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.09765414716386604</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-27.8022477075037</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-17.59463268895477</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-17.38626169391643</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-27.00370152054597</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
+        <v>-0.7355869064404832</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>12.23666031974166</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.673652574205038</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.23960880562823</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>20.77990272510416</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.227600279015077</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.257855993518094</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="n">
+        <v>1.405014090350534</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1039,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
